--- a/Chennai-January-2026.xlsx
+++ b/Chennai-January-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="51">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Chennai</t>
   </si>
   <si>
@@ -142,16 +145,13 @@
     <t>TN14AK9389</t>
   </si>
   <si>
-    <t>DZIRE CNG</t>
-  </si>
-  <si>
     <t>DZIRE</t>
   </si>
   <si>
-    <t>Crysta</t>
-  </si>
-  <si>
-    <t>Citron</t>
+    <t>CRYSTA</t>
+  </si>
+  <si>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>30/05/2023</t>
@@ -528,10 +528,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -610,25 +610,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>48</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G2" s="2">
         <v>44205</v>
@@ -691,21 +694,21 @@
         <v>54.07</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>49</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
         <v>43</v>
@@ -771,21 +774,21 @@
         <v>28.97</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
         <v>44</v>
@@ -851,21 +854,21 @@
         <v>9.779999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
         <v>44</v>
@@ -931,21 +934,21 @@
         <v>49.62</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
         <v>44</v>
@@ -1011,21 +1014,21 @@
         <v>49.75</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2026</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
         <v>44</v>
@@ -1091,21 +1094,21 @@
         <v>56.45</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>54</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2026</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
         <v>44</v>
@@ -1171,21 +1174,21 @@
         <v>58.95</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2026</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
         <v>44</v>
@@ -1251,21 +1254,21 @@
         <v>42.46</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2026</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
         <v>44</v>
@@ -1331,21 +1334,21 @@
         <v>49.74</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2026</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
         <v>44</v>
@@ -1411,21 +1414,21 @@
         <v>14.96</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>58</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2026</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
         <v>44</v>
@@ -1491,21 +1494,21 @@
         <v>17.44</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2026</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
         <v>44</v>
@@ -1571,21 +1574,21 @@
         <v>57.72</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2026</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
         <v>44</v>
@@ -1651,21 +1654,21 @@
         <v>61.1</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>61</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2026</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
         <v>45</v>
